--- a/InputData/trans/PTFURfE/Perc Trans Fuel Use Reduction for Elec.xlsx
+++ b/InputData/trans/PTFURfE/Perc Trans Fuel Use Reduction for Elec.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28521"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipM\InputData\trans\PTFURfE\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_256AC4A4FBC51A161F9A9D9F1270DEB9A62485EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="20115" windowHeight="12075"/>
+    <workbookView xWindow="360" yWindow="105" windowWidth="20115" windowHeight="12075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -17,16 +18,50 @@
     <sheet name="HDVs, Rail" sheetId="2" r:id="rId3"/>
     <sheet name="PTFURfE" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="51">
   <si>
+    <t>PTFURfE Percentage Transportation Fuel Use Reduction for Electricity</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>LDVs</t>
+  </si>
+  <si>
+    <t>U.S. Department of Energy, U.S. EPA</t>
+  </si>
+  <si>
+    <t>All-Electric Vehicles (EVs)</t>
+  </si>
+  <si>
+    <t>http://www.fueleconomy.gov/feg/evtech.shtml</t>
+  </si>
+  <si>
+    <t>HDVs, Rail</t>
+  </si>
+  <si>
     <t>M. J. Bradley &amp; Associates</t>
   </si>
   <si>
@@ -39,88 +74,109 @@
     <t>Page 4, Table 1.1</t>
   </si>
   <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>For vehicle types that can use electricity, this variable specifies the percentage</t>
+  </si>
+  <si>
+    <t>reduction in fuel use (on a BTU basis) relative to the typical fuel type for that vehicle</t>
+  </si>
+  <si>
+    <t>type (e.g. gasoline for LDVs, diesel for HDVs, etc.) due to the fact that electricity</t>
+  </si>
+  <si>
+    <t>can be converted into work more efficiently than other fuel types.</t>
+  </si>
+  <si>
+    <t>For the LCFS to work correctly, all on-road modes need to have the same value, so we</t>
+  </si>
+  <si>
+    <t>use the passenger LDVs value for all on-road modes.  (It is very close to the calculated</t>
+  </si>
+  <si>
+    <t>passenger HDVs value in any case.)</t>
+  </si>
+  <si>
+    <t>Aircraft and ships are assumed to be the same as rail, since they all use large engines</t>
+  </si>
+  <si>
+    <t>intended to move heavy craft.</t>
+  </si>
+  <si>
+    <t>Vehicle Type</t>
+  </si>
+  <si>
+    <t>Fuel Type</t>
+  </si>
+  <si>
+    <t>Efficiency (Low)</t>
+  </si>
+  <si>
+    <t>Efficiency (High)</t>
+  </si>
+  <si>
+    <t>Efficiency (Avg)</t>
+  </si>
+  <si>
+    <t>gasoline</t>
+  </si>
+  <si>
+    <t>electricity</t>
+  </si>
+  <si>
+    <t>Percentage Fuel Use Reduction</t>
+  </si>
+  <si>
     <t>Model Vehicle Type</t>
   </si>
   <si>
+    <t>Corresponding Vehicle Type from Key (page 1)</t>
+  </si>
+  <si>
+    <t>Corresponding Vehicle Type from Table 1.1</t>
+  </si>
+  <si>
     <t>Energy Use (BTU/passenger*mile)</t>
   </si>
   <si>
     <t>passenger HDV</t>
   </si>
   <si>
-    <t>Fuel Type</t>
-  </si>
-  <si>
     <t>petroleum diesel</t>
   </si>
   <si>
     <t>Urban Transit Bus</t>
   </si>
   <si>
-    <t>electricity</t>
+    <t>Transit Bus</t>
   </si>
   <si>
     <t>Electric Trolley Bus</t>
   </si>
   <si>
+    <t>Trolley Bus</t>
+  </si>
+  <si>
     <t>passenger rail</t>
   </si>
   <si>
+    <t>Commuter Rail</t>
+  </si>
+  <si>
     <t>Heavy Urban Rail</t>
   </si>
   <si>
-    <t>Commuter Rail</t>
-  </si>
-  <si>
-    <t>Corresponding Vehicle Type from Key (page 1)</t>
-  </si>
-  <si>
-    <t>Corresponding Vehicle Type from Table 1.1</t>
-  </si>
-  <si>
-    <t>Transit Bus</t>
-  </si>
-  <si>
-    <t>Trolley Bus</t>
-  </si>
-  <si>
     <t>Heavy Rail</t>
   </si>
   <si>
-    <t>LDVs</t>
-  </si>
-  <si>
-    <t>Percentage Fuel Use Reduction</t>
-  </si>
-  <si>
-    <t>U.S. Department of Energy, U.S. EPA</t>
-  </si>
-  <si>
-    <t>All-Electric Vehicles (EVs)</t>
-  </si>
-  <si>
-    <t>http://www.fueleconomy.gov/feg/evtech.shtml</t>
-  </si>
-  <si>
-    <t>Vehicle Type</t>
-  </si>
-  <si>
-    <t>Efficiency (Low)</t>
-  </si>
-  <si>
-    <t>Efficiency (High)</t>
-  </si>
-  <si>
-    <t>Efficiency (Avg)</t>
-  </si>
-  <si>
-    <t>gasoline</t>
-  </si>
-  <si>
-    <t>HDVs, Rail</t>
-  </si>
-  <si>
-    <t>PTFURfE Percentage Transportation Fuel Use Reduction for Electricity</t>
+    <t>Percentage Reduction (dimensionless)</t>
+  </si>
+  <si>
+    <t>Passengers</t>
+  </si>
+  <si>
+    <t>Freight</t>
   </si>
   <si>
     <t>HDVs</t>
@@ -136,56 +192,17 @@
   </si>
   <si>
     <t>motorbikes</t>
-  </si>
-  <si>
-    <t>Passengers</t>
-  </si>
-  <si>
-    <t>Freight</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>For the LCFS to work correctly, all on-road modes need to have the same value, so we</t>
-  </si>
-  <si>
-    <t>use the passenger LDVs value for all on-road modes.  (It is very close to the calculated</t>
-  </si>
-  <si>
-    <t>passenger HDVs value in any case.)</t>
-  </si>
-  <si>
-    <t>For vehicle types that can use electricity, this variable specifies the percentage</t>
-  </si>
-  <si>
-    <t>reduction in fuel use (on a BTU basis) relative to the typical fuel type for that vehicle</t>
-  </si>
-  <si>
-    <t>type (e.g. gasoline for LDVs, diesel for HDVs, etc.) due to the fact that electricity</t>
-  </si>
-  <si>
-    <t>can be converted into work more efficiently than other fuel types.</t>
-  </si>
-  <si>
-    <t>Percentage Reduction (dimensionless)</t>
-  </si>
-  <si>
-    <t>Aircraft and ships are assumed to be the same as rail, since they all use large engines</t>
-  </si>
-  <si>
-    <t>intended to move heavy craft.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,7 +268,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -269,7 +286,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -290,9 +306,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -330,9 +346,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -367,7 +383,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,7 +418,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -575,133 +591,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="72.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="B5" s="2">
         <v>2014</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="B7" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="B12" s="2">
         <v>2007</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="B14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1"/>
-    <hyperlink ref="B7" r:id="rId2"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId3"/>
@@ -709,38 +722,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="15.7109375" customWidth="1"/>
     <col min="3" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>30</v>
       </c>
       <c r="C2" s="6">
         <v>0.17</v>
@@ -753,12 +766,12 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C3" s="6">
         <v>0.59</v>
@@ -771,17 +784,17 @@
         <v>0.60499999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30">
       <c r="A5" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="8" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B6" s="7">
         <f>(E3-E2)/E3</f>
@@ -794,9 +807,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
@@ -804,111 +817,111 @@
     <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30">
       <c r="A1" s="4" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2">
         <v>4245</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2">
         <v>1321</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2">
         <v>1608</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2">
         <v>889</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="4" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B8" s="7">
         <f>(E2-E3)/E2</f>
         <v>0.68881036513545346</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7">
         <f>(E4-E5)/E4</f>
@@ -922,32 +935,32 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="45">
       <c r="A1" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B2" s="9">
         <f>LDVs!B6</f>
@@ -958,9 +971,9 @@
         <v>0.68595041322314043</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B3" s="9">
         <f>$B$2</f>
@@ -971,9 +984,9 @@
         <v>0.68595041322314043</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B4" s="9">
         <f>B5</f>
@@ -984,9 +997,9 @@
         <v>0.44713930348258707</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B5" s="9">
         <f>'HDVs, Rail'!B9</f>
@@ -997,9 +1010,9 @@
         <v>0.44713930348258707</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="9">
         <f>B5</f>
@@ -1010,9 +1023,9 @@
         <v>0.44713930348258707</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B7" s="9">
         <f>$B$2</f>
@@ -1027,4 +1040,175 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEBC22DD-01C5-446E-A03A-8415A89C35F7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71D8C0E7-E5A6-424C-9254-67A0802407E8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0700419-774B-4063-BD69-CA8C5C903D44}"/>
 </file>